--- a/public/paper-sample-cost-breakdown.xlsx
+++ b/public/paper-sample-cost-breakdown.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="166">
   <si>
     <t>{{발행처로고}}</t>
   </si>
@@ -447,6 +447,12 @@
     <t>집계. 합계 · 개수 · 평균 셋만 됩니다. 쉼표로 여러 열을 더할 수 있습니다.</t>
   </si>
   <si>
+    <t>{{들여:품목.품명}}</t>
+  </si>
+  <si>
+    <t>트리 줄. 그 줄의 «깊이»만큼 글자가 밀립니다. 보통 품명 칸 하나에만 붙입니다 — 수량·단가는 제 열에 그대로 서야 세로로 읽힙니다.</t>
+  </si>
+  <si>
     <t>{{@쪽}} {{@총쪽}}</t>
   </si>
   <si>
@@ -471,10 +477,25 @@
     <t>묶음이 바뀔 때 / 끝날 때 한 번. 소계 자리입니다.</t>
   </si>
   <si>
+    <t>트리에서는 「그룹머리」 없이 「그룹꼬리」만 적어도 됩니다 — 깊이 1인 줄이 다시 나오는 것이 곧 앞 묶음의 끝이라, 묶음 기준을 구조가 이미 말하고 있습니다.</t>
+  </si>
+  <si>
     <t>이 줄이 데이터 개수만큼 늘어납니다.</t>
   </si>
   <si>
     <t>마지막 쪽에만 나옵니다.</t>
+  </si>
+  <si>
+    <t>줄마다 깊이가 다른 표</t>
+  </si>
+  <si>
+    <t>내역서처럼 「주방 › 상부장 › 옵션1」이 딸리는 표는, 깊이를 담을 열을 하나 만들고 「필드」 시트에서 그 열의 종류를 «깊이»로 둡니다(1이 가장 얕습니다).</t>
+  </si>
+  <si>
+    <t>그 열은 종이에 안 찍힙니다 — 들여쓰기와 소계 경계가 읽어 가는 축입니다. 서식에는 «반복» 줄이 하나만 있고, 몇 줄이 될지는 값이 정합니다.</t>
+  </si>
+  <si>
+    <t>중간 줄도 자기 금액을 갖습니다(상부장은 옵션의 합이 아닙니다). 소계는 그 묶음에 딸린 모든 줄을 더하므로, 부모를 자식의 합으로 넣으면 두 번 더해집니다.</t>
   </si>
   <si>
     <t>표준 머리에 있는 것</t>
@@ -2816,10 +2837,10 @@
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="C10:C80">
-      <formula1>"글자,숫자,금액,날짜,여러 줄,선택,예아니오,이미지"</formula1>
+      <formula1>"글자,숫자,금액,날짜,여러 줄,선택,예아니오,이미지,깊이"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C2:C80">
-      <formula1>"글자,숫자,금액,날짜,여러 줄,선택,예아니오,이미지"</formula1>
+      <formula1>"글자,숫자,금액,날짜,여러 줄,선택,예아니오,이미지,깊이"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D10:D80">
       <formula1>"필수"</formula1>
@@ -2835,7 +2856,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2948,39 +2969,39 @@
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="B16" s="24" t="s">
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="23" t="s">
         <v>147</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
-        <v>23</v>
+        <v>148</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
-        <v>149</v>
+        <v>23</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>150</v>
@@ -2988,34 +3009,34 @@
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
-        <v>38</v>
+        <v>151</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>29</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3023,15 +3044,15 @@
         <v>29</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>155</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3039,7 +3060,7 @@
         <v>29</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3047,15 +3068,71 @@
         <v>29</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="24" t="s">
-        <v>157</v>
+        <v>29</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>158</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/public/paper-sample-cost-breakdown.xlsx
+++ b/public/paper-sample-cost-breakdown.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="170">
   <si>
     <t>{{발행처로고}}</t>
   </si>
@@ -453,6 +453,12 @@
     <t>트리 줄. 그 줄의 «깊이»만큼 글자가 밀립니다. 보통 품명 칸 하나에만 붙입니다 — 수량·단가는 제 열에 그대로 서야 세로로 읽힙니다.</t>
   </si>
   <si>
+    <t>{{번호:품목.품명}}</t>
+  </si>
+  <si>
+    <t>구획 제목의 번호 — 「1. 주방」 「2. 후드」. 묶음을 여는 줄에만 붙고, 번호는 데이터가 아니라 그 표에서의 «자리»에서 나옵니다.</t>
+  </si>
+  <si>
     <t>{{@쪽}} {{@총쪽}}</t>
   </si>
   <si>
@@ -480,6 +486,9 @@
     <t>트리에서는 「그룹머리」 없이 「그룹꼬리」만 적어도 됩니다 — 깊이 1인 줄이 다시 나오는 것이 곧 앞 묶음의 끝이라, 묶음 기준을 구조가 이미 말하고 있습니다.</t>
   </si>
   <si>
+    <t>「열머리」를 「그룹머리」 «아래»에 두면 구획마다 열머리가 다시 납니다. «위»에 두면 표 전체에 한 번입니다 — 적힌 순서가 곧 발화 순서입니다.</t>
+  </si>
+  <si>
     <t>이 줄이 데이터 개수만큼 늘어납니다.</t>
   </si>
   <si>
@@ -495,7 +504,10 @@
     <t>그 열은 종이에 안 찍힙니다 — 들여쓰기와 소계 경계가 읽어 가는 축입니다. 서식에는 «반복» 줄이 하나만 있고, 몇 줄이 될지는 값이 정합니다.</t>
   </si>
   <si>
-    <t>중간 줄도 자기 금액을 갖습니다(상부장은 옵션의 합이 아닙니다). 소계는 그 묶음에 딸린 모든 줄을 더하므로, 부모를 자식의 합으로 넣으면 두 번 더해집니다.</t>
+    <t>깊이 1을 «구획 제목»으로 쓰면(「그룹머리」로 두면) 그 줄은 반복에서 빠집니다 — 제목이 가져가므로 같은 이름이 두 번 나오지 않습니다. 이때 제목 줄은 자기 금액을 갖지 않고, 그 구획의 수는 소계가 말합니다.</t>
+  </si>
+  <si>
+    <t>들여쓰기는 «그려지는 줄 중 가장 얕은 깊이»가 기준입니다. 제목이 깊이 1을 가져가면 깊이 2가 기준선이 되어 표가 통째로 밀려 들어가지 않습니다.</t>
   </si>
   <si>
     <t>표준 머리에 있는 것</t>
@@ -2856,7 +2868,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2977,39 +2989,39 @@
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>29</v>
+        <v>147</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="B17" s="24" t="s">
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
         <v>149</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
-        <v>23</v>
+        <v>150</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>152</v>
@@ -3017,42 +3029,42 @@
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
-        <v>29</v>
+        <v>153</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="24" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>29</v>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3060,15 +3072,15 @@
         <v>29</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>158</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3076,7 +3088,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3084,15 +3096,15 @@
         <v>29</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>29</v>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3100,7 +3112,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3108,15 +3120,15 @@
         <v>29</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>163</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3124,15 +3136,39 @@
         <v>29</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>29</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="24" t="s">
-        <v>164</v>
+        <v>29</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>165</v>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/public/paper-sample-cost-breakdown.xlsx
+++ b/public/paper-sample-cost-breakdown.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="172">
   <si>
     <t>{{발행처로고}}</t>
   </si>
@@ -427,6 +427,12 @@
   </si>
   <si>
     <t>기본 18pt(=한 칸). 높은 칸은 36pt·54pt처럼 18의 배수로 둡니다.</t>
+  </si>
+  <si>
+    <t>세로 정렬</t>
+  </si>
+  <si>
+    <t>엑셀은 세로 정렬을 안 정하면 «아래»에 붙여 그리지만, 인쇄물은 «가운데»로 나갑니다. 엑셀 화면과 결과를 맞추려면 세로 정렬을 «가운데»로 지정해 두세요(결과가 바뀌지는 않습니다).</t>
   </si>
   <si>
     <t>값이 들어갈 자리</t>
@@ -2868,7 +2874,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2933,31 +2939,31 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>29</v>
+        <v>137</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="24" t="s">
         <v>138</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>139</v>
+        <v>3</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>140</v>
@@ -2997,39 +3003,39 @@
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>29</v>
+        <v>149</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="B18" s="24" t="s">
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
         <v>151</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>154</v>
@@ -3037,10 +3043,10 @@
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3048,47 +3054,47 @@
         <v>29</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="24" t="s">
         <v>160</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3096,7 +3102,7 @@
         <v>29</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3104,7 +3110,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3112,7 +3118,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3120,23 +3126,23 @@
         <v>29</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="24" t="s">
         <v>165</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3144,7 +3150,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3152,7 +3158,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -3160,15 +3166,23 @@
         <v>29</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>29</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="24" t="s">
-        <v>168</v>
+        <v>29</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>169</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="B38" s="24" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
